--- a/files/MCQs.xlsx
+++ b/files/MCQs.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10311"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7F7D75-FD1B-447F-A578-F6FCFE6140E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AB3D14-A4B6-DD47-9E7B-86BC68624636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation" sheetId="1" r:id="rId1"/>
@@ -9937,10 +9937,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10266,25 +10262,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG251"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" customWidth="1"/>
-    <col min="4" max="4" width="43.28515625" customWidth="1"/>
-    <col min="5" max="5" width="53.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="165.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" customWidth="1"/>
-    <col min="11" max="11" width="9.85546875" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" customWidth="1"/>
+    <col min="4" max="4" width="43.33203125" customWidth="1"/>
+    <col min="5" max="5" width="53.5" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="165.6640625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
     <col min="14" max="25" width="5" customWidth="1"/>
-    <col min="26" max="26" width="20.28515625" customWidth="1"/>
+    <col min="26" max="26" width="20.33203125" customWidth="1"/>
     <col min="27" max="31" width="5" customWidth="1"/>
-    <col min="32" max="32" width="5.42578125" customWidth="1"/>
+    <col min="32" max="32" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -10382,7 +10378,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -10480,7 +10476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -10578,7 +10574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -10676,7 +10672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
@@ -10774,7 +10770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -10872,7 +10868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:32" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -10970,7 +10966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
@@ -11068,7 +11064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
@@ -11166,7 +11162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
@@ -11264,7 +11260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
@@ -11362,7 +11358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
@@ -11460,7 +11456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1</v>
       </c>
@@ -11558,7 +11554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
@@ -11656,7 +11652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
@@ -11754,7 +11750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1</v>
       </c>
@@ -11852,7 +11848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
@@ -11950,7 +11946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1</v>
       </c>
@@ -12048,7 +12044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1</v>
       </c>
@@ -12146,7 +12142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
@@ -12244,7 +12240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
@@ -12342,7 +12338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1</v>
       </c>
@@ -12440,7 +12436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
@@ -12538,7 +12534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1</v>
       </c>
@@ -12636,7 +12632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1</v>
       </c>
@@ -12734,7 +12730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1</v>
       </c>
@@ -12832,7 +12828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1</v>
       </c>
@@ -12930,7 +12926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1</v>
       </c>
@@ -13022,7 +13018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1</v>
       </c>
@@ -13120,7 +13116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1</v>
       </c>
@@ -13218,7 +13214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>1</v>
       </c>
@@ -13316,7 +13312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>1</v>
       </c>
@@ -13414,7 +13410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>1</v>
       </c>
@@ -13512,7 +13508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -13610,7 +13606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>1</v>
       </c>
@@ -13708,7 +13704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>1</v>
       </c>
@@ -13806,7 +13802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>1</v>
       </c>
@@ -13904,7 +13900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>1</v>
       </c>
@@ -14002,7 +13998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>1</v>
       </c>
@@ -14100,7 +14096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>1</v>
       </c>
@@ -14198,7 +14194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3">
         <v>1</v>
       </c>
@@ -14296,7 +14292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>1</v>
       </c>
@@ -14394,7 +14390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3">
         <v>1</v>
       </c>
@@ -14492,7 +14488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>1</v>
       </c>
@@ -14590,7 +14586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3">
         <v>1</v>
       </c>
@@ -14688,7 +14684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>1</v>
       </c>
@@ -14786,7 +14782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>1</v>
       </c>
@@ -14884,7 +14880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>1</v>
       </c>
@@ -14982,7 +14978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>1</v>
       </c>
@@ -15080,7 +15076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>1</v>
       </c>
@@ -15178,7 +15174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>1</v>
       </c>
@@ -15276,7 +15272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>1</v>
       </c>
@@ -15377,7 +15373,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>1</v>
       </c>
@@ -15475,7 +15471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3">
         <v>1</v>
       </c>
@@ -15573,7 +15569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>1</v>
       </c>
@@ -15674,7 +15670,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>1</v>
       </c>
@@ -15772,7 +15768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>1</v>
       </c>
@@ -15873,7 +15869,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>1</v>
       </c>
@@ -15971,7 +15967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>1</v>
       </c>
@@ -16069,7 +16065,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>1</v>
       </c>
@@ -16167,7 +16163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>1</v>
       </c>
@@ -16265,7 +16261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3">
         <v>1</v>
       </c>
@@ -16363,7 +16359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3">
         <v>1</v>
       </c>
@@ -16461,7 +16457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3">
         <v>1</v>
       </c>
@@ -16559,7 +16555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3">
         <v>1</v>
       </c>
@@ -16657,7 +16653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -16755,7 +16751,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>1</v>
       </c>
@@ -16853,7 +16849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3">
         <v>1</v>
       </c>
@@ -16951,7 +16947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3">
         <v>1</v>
       </c>
@@ -17049,7 +17045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3">
         <v>1</v>
       </c>
@@ -17150,7 +17146,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="71" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3">
         <v>1</v>
       </c>
@@ -17248,7 +17244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3">
         <v>1</v>
       </c>
@@ -17346,7 +17342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>1</v>
       </c>
@@ -17444,7 +17440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>1</v>
       </c>
@@ -17542,7 +17538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3">
         <v>1</v>
       </c>
@@ -17643,7 +17639,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>1</v>
       </c>
@@ -17741,7 +17737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>1</v>
       </c>
@@ -17839,7 +17835,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>1</v>
       </c>
@@ -17937,7 +17933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3">
         <v>1</v>
       </c>
@@ -18035,7 +18031,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>1</v>
       </c>
@@ -18133,7 +18129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>1</v>
       </c>
@@ -18231,7 +18227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>1</v>
       </c>
@@ -18329,7 +18325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>1</v>
       </c>
@@ -18427,7 +18423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>1</v>
       </c>
@@ -18525,7 +18521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3">
         <v>1</v>
       </c>
@@ -18623,7 +18619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>1</v>
       </c>
@@ -18721,7 +18717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3">
         <v>1</v>
       </c>
@@ -18819,7 +18815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>1</v>
       </c>
@@ -18917,7 +18913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3">
         <v>1</v>
       </c>
@@ -19015,7 +19011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>1</v>
       </c>
@@ -19113,7 +19109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3">
         <v>1</v>
       </c>
@@ -19211,7 +19207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>1</v>
       </c>
@@ -19309,7 +19305,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>1</v>
       </c>
@@ -19407,7 +19403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3">
         <v>1</v>
       </c>
@@ -19505,7 +19501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>1</v>
       </c>
@@ -19603,7 +19599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3">
         <v>1</v>
       </c>
@@ -19701,7 +19697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>1</v>
       </c>
@@ -19799,7 +19795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -19897,7 +19893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3">
         <v>1</v>
       </c>
@@ -19995,7 +19991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>1</v>
       </c>
@@ -20093,7 +20089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>1</v>
       </c>
@@ -20191,7 +20187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>1</v>
       </c>
@@ -20289,7 +20285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3">
         <v>1</v>
       </c>
@@ -20387,7 +20383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="3">
         <v>1</v>
       </c>
@@ -20485,7 +20481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A105" s="3">
         <v>1</v>
       </c>
@@ -20583,7 +20579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>1</v>
       </c>
@@ -20681,7 +20677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>1</v>
       </c>
@@ -20779,7 +20775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>1</v>
       </c>
@@ -20877,7 +20873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>1</v>
       </c>
@@ -20975,7 +20971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>1</v>
       </c>
@@ -21073,7 +21069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>1</v>
       </c>
@@ -21171,7 +21167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A112" s="3">
         <v>1</v>
       </c>
@@ -21269,7 +21265,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A113" s="3">
         <v>1</v>
       </c>
@@ -21370,7 +21366,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>1</v>
       </c>
@@ -21471,7 +21467,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>1</v>
       </c>
@@ -21569,7 +21565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>1</v>
       </c>
@@ -21667,7 +21663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" s="3">
         <v>1</v>
       </c>
@@ -21765,7 +21761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A118" s="3">
         <v>1</v>
       </c>
@@ -21866,7 +21862,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="119" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>1</v>
       </c>
@@ -21964,7 +21960,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>1</v>
       </c>
@@ -22062,7 +22058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>1</v>
       </c>
@@ -22160,7 +22156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>1</v>
       </c>
@@ -22261,7 +22257,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="123" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>1</v>
       </c>
@@ -22359,7 +22355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>1</v>
       </c>
@@ -22457,7 +22453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>1</v>
       </c>
@@ -22558,7 +22554,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="126" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>1</v>
       </c>
@@ -22656,7 +22652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>1</v>
       </c>
@@ -22757,7 +22753,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>1</v>
       </c>
@@ -22858,7 +22854,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="129" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>1</v>
       </c>
@@ -22956,7 +22952,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -23054,7 +23050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>1</v>
       </c>
@@ -23152,7 +23148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>1</v>
       </c>
@@ -23250,7 +23246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>1</v>
       </c>
@@ -23348,7 +23344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>1</v>
       </c>
@@ -23446,7 +23442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>1</v>
       </c>
@@ -23544,7 +23540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>1</v>
       </c>
@@ -23642,7 +23638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A137" s="3">
         <v>1</v>
       </c>
@@ -23740,7 +23736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A138" s="3">
         <v>1</v>
       </c>
@@ -23838,7 +23834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A139" s="3">
         <v>1</v>
       </c>
@@ -23936,7 +23932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>1</v>
       </c>
@@ -24034,7 +24030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>1</v>
       </c>
@@ -24132,7 +24128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A142" s="3">
         <v>1</v>
       </c>
@@ -24233,7 +24229,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="143" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A143" s="3">
         <v>1</v>
       </c>
@@ -24331,7 +24327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A144" s="3">
         <v>1</v>
       </c>
@@ -24432,7 +24428,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="145" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>1</v>
       </c>
@@ -24533,7 +24529,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="146" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A146" s="3">
         <v>1</v>
       </c>
@@ -24631,7 +24627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>1</v>
       </c>
@@ -24729,7 +24725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>1</v>
       </c>
@@ -24830,7 +24826,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="149" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>1</v>
       </c>
@@ -24928,7 +24924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>1</v>
       </c>
@@ -25026,7 +25022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>1</v>
       </c>
@@ -25124,7 +25120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A152" s="3">
         <v>1</v>
       </c>
@@ -25222,7 +25218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A153" s="3">
         <v>1</v>
       </c>
@@ -25320,7 +25316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>1</v>
       </c>
@@ -25418,7 +25414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A155" s="3">
         <v>1</v>
       </c>
@@ -25516,7 +25512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A156" s="3">
         <v>1</v>
       </c>
@@ -25614,7 +25610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>1</v>
       </c>
@@ -25712,7 +25708,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>1</v>
       </c>
@@ -25810,7 +25806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>1</v>
       </c>
@@ -25908,7 +25904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3">
         <v>1</v>
       </c>
@@ -26006,7 +26002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A161" s="3">
         <v>1</v>
       </c>
@@ -26104,7 +26100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -26202,7 +26198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>1</v>
       </c>
@@ -26300,7 +26296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>1</v>
       </c>
@@ -26398,7 +26394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A165" s="3">
         <v>1</v>
       </c>
@@ -26496,7 +26492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A166" s="3">
         <v>1</v>
       </c>
@@ -26594,7 +26590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>1</v>
       </c>
@@ -26692,7 +26688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>1</v>
       </c>
@@ -26790,7 +26786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>1</v>
       </c>
@@ -26888,7 +26884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>1</v>
       </c>
@@ -26986,7 +26982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>1</v>
       </c>
@@ -26997,13 +26993,13 @@
         <v>2123</v>
       </c>
       <c r="D171">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E171" t="s">
         <v>2192</v>
       </c>
       <c r="F171">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G171" t="s">
         <v>2193</v>
@@ -27084,7 +27080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>1</v>
       </c>
@@ -27095,13 +27091,13 @@
         <v>2123</v>
       </c>
       <c r="D172">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E172" t="s">
         <v>2192</v>
       </c>
       <c r="F172">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G172" t="s">
         <v>2206</v>
@@ -27182,7 +27178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>1</v>
       </c>
@@ -27193,13 +27189,13 @@
         <v>2123</v>
       </c>
       <c r="D173">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E173" t="s">
         <v>2192</v>
       </c>
       <c r="F173">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G173" t="s">
         <v>2219</v>
@@ -27283,7 +27279,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="174" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>1</v>
       </c>
@@ -27294,13 +27290,13 @@
         <v>2123</v>
       </c>
       <c r="D174">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E174" t="s">
         <v>2192</v>
       </c>
       <c r="F174">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="G174" t="s">
         <v>2232</v>
@@ -27381,7 +27377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A175" s="3">
         <v>1</v>
       </c>
@@ -27479,7 +27475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>1</v>
       </c>
@@ -27577,7 +27573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>1</v>
       </c>
@@ -27675,7 +27671,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>1</v>
       </c>
@@ -27773,7 +27769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>1</v>
       </c>
@@ -27871,7 +27867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>1</v>
       </c>
@@ -27969,7 +27965,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>1</v>
       </c>
@@ -28067,7 +28063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>1</v>
       </c>
@@ -28165,7 +28161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A183" s="3">
         <v>1</v>
       </c>
@@ -28263,7 +28259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>1</v>
       </c>
@@ -28361,7 +28357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A185" s="3">
         <v>1</v>
       </c>
@@ -28459,7 +28455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>1</v>
       </c>
@@ -28557,7 +28553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>1</v>
       </c>
@@ -28655,7 +28651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>1</v>
       </c>
@@ -28753,7 +28749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>1</v>
       </c>
@@ -28851,7 +28847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A190" s="3">
         <v>1</v>
       </c>
@@ -28949,7 +28945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>1</v>
       </c>
@@ -29047,7 +29043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>1</v>
       </c>
@@ -29145,7 +29141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A193" s="3">
         <v>1</v>
       </c>
@@ -29243,7 +29239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -29341,7 +29337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>1</v>
       </c>
@@ -29439,7 +29435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A196" s="3">
         <v>1</v>
       </c>
@@ -29537,7 +29533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>1</v>
       </c>
@@ -29635,7 +29631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>1</v>
       </c>
@@ -29733,7 +29729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>1</v>
       </c>
@@ -29831,7 +29827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>1</v>
       </c>
@@ -29929,7 +29925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>1</v>
       </c>
@@ -30027,7 +30023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>1</v>
       </c>
@@ -30125,7 +30121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>1</v>
       </c>
@@ -30223,7 +30219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>1</v>
       </c>
@@ -30321,7 +30317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>1</v>
       </c>
@@ -30419,7 +30415,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>1</v>
       </c>
@@ -30517,7 +30513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>1</v>
       </c>
@@ -30615,7 +30611,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>1</v>
       </c>
@@ -30713,7 +30709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>1</v>
       </c>
@@ -30811,7 +30807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>1</v>
       </c>
@@ -30909,7 +30905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>1</v>
       </c>
@@ -31007,7 +31003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>1</v>
       </c>
@@ -31105,7 +31101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>1</v>
       </c>
@@ -31203,7 +31199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>1</v>
       </c>
@@ -31301,7 +31297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>1</v>
       </c>
@@ -31399,7 +31395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A216" s="3">
         <v>1</v>
       </c>
@@ -31497,7 +31493,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A217" s="3">
         <v>1</v>
       </c>
@@ -31595,7 +31591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>1</v>
       </c>
@@ -31693,7 +31689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>1</v>
       </c>
@@ -31791,7 +31787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>1</v>
       </c>
@@ -31889,7 +31885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A221" s="3">
         <v>1</v>
       </c>
@@ -31987,7 +31983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>1</v>
       </c>
@@ -32085,7 +32081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A223" s="3">
         <v>1</v>
       </c>
@@ -32183,7 +32179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:32" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A224" s="3">
         <v>1</v>
       </c>
@@ -32281,7 +32277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A225" s="3">
         <v>1</v>
       </c>
@@ -32379,7 +32375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A226" s="3">
         <v>1</v>
       </c>
@@ -32477,7 +32473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A227" s="3">
         <v>1</v>
       </c>
@@ -32578,7 +32574,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="228" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A228" s="3">
         <v>1</v>
       </c>
@@ -32676,7 +32672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>1</v>
       </c>
@@ -32774,7 +32770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>1</v>
       </c>
@@ -32872,7 +32868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A231" s="3">
         <v>1</v>
       </c>
@@ -32970,7 +32966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A232" s="3">
         <v>1</v>
       </c>
@@ -33068,7 +33064,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>1</v>
       </c>
@@ -33166,7 +33162,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>1</v>
       </c>
@@ -33264,7 +33260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A235" s="3">
         <v>1</v>
       </c>
@@ -33362,7 +33358,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>1</v>
       </c>
@@ -33460,7 +33456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A237" s="3">
         <v>1</v>
       </c>
@@ -33561,7 +33557,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="238" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>1</v>
       </c>
@@ -33659,7 +33655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>1</v>
       </c>
@@ -33757,7 +33753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A240" s="3">
         <v>1</v>
       </c>
@@ -33855,7 +33851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>1</v>
       </c>
@@ -33953,7 +33949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>1</v>
       </c>
@@ -34051,7 +34047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>1</v>
       </c>
@@ -34149,7 +34145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>1</v>
       </c>
@@ -34247,7 +34243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>1</v>
       </c>
@@ -34345,7 +34341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A246" s="3">
         <v>1</v>
       </c>
@@ -34443,7 +34439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>1</v>
       </c>
@@ -34544,7 +34540,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="248" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:33" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A248" s="3">
         <v>1</v>
       </c>
@@ -34642,7 +34638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>1</v>
       </c>
@@ -34740,7 +34736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>1</v>
       </c>
@@ -34838,7 +34834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>1</v>
       </c>

--- a/files/MCQs.xlsx
+++ b/files/MCQs.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10311"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AB3D14-A4B6-DD47-9E7B-86BC68624636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A846D8C8-FC02-5840-A028-A4C25BAB7F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4050" uniqueCount="3261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4050" uniqueCount="3262">
   <si>
     <t>Approved</t>
   </si>
@@ -9827,6 +9827,9 @@
   </si>
   <si>
     <t>Python erlaubt keine Sonderzeichen wie '@' oder '%' innerhalb von Variablennamen. Diese sind in Variablennamen nicht zulässig.</t>
+  </si>
+  <si>
+    <t>Tupel</t>
   </si>
 </sst>
 </file>
@@ -27685,10 +27688,10 @@
         <v>39</v>
       </c>
       <c r="E178" t="s">
-        <v>2245</v>
+        <v>3261</v>
       </c>
       <c r="F178">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G178" t="s">
         <v>2285</v>
@@ -28472,7 +28475,7 @@
         <v>2391</v>
       </c>
       <c r="F186">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G186" t="s">
         <v>2392</v>
@@ -28570,7 +28573,7 @@
         <v>2391</v>
       </c>
       <c r="F187">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G187" t="s">
         <v>2401</v>

--- a/files/MCQs.xlsx
+++ b/files/MCQs.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10311"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E5F065-4398-3145-9545-E58D7C7311D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9E2BC9-9509-3042-845B-9FD110941BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="760" windowWidth="30240" windowHeight="17720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation" sheetId="1" r:id="rId1"/>
@@ -22868,7 +22868,7 @@
         <v>1153</v>
       </c>
       <c r="F155">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="G155" t="s">
         <v>1523</v>
@@ -22967,7 +22967,7 @@
         <v>1153</v>
       </c>
       <c r="F156">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="G156" t="s">
         <v>1531</v>
@@ -23065,7 +23065,7 @@
         <v>1153</v>
       </c>
       <c r="F157">
-        <v>206</v>
+        <v>85</v>
       </c>
       <c r="G157" t="s">
         <v>1544</v>
